--- a/mixs-templates/Misag_plus_combinations/MisagHydrocarbonResourcesCores.xlsx
+++ b/mixs-templates/Misag_plus_combinations/MisagHydrocarbonResourcesCores.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ1"/>
+  <dimension ref="A1:EL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,505 +614,515 @@
       </c>
       <c r="AN1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>sort_tech</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>wga_amp_appr</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>sc_lysis_approach</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>hcr</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>hc_produced</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>basin</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>reservoir</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>hcr_temp</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>tvdss_of_hcr_temp</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>hcr_pressure</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>tvdss_of_hcr_press</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>permeability</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>porosity</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>lithology</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>depos_env</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>hcr_geol_age</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>owc_tvdss</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>hcr_fw_salinity</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>sulfate_fw</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>vfa_fw</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>sr_kerog_type</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>sr_lithology</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>sr_dep_env</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>sr_geol_age</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>samp_well_name</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>samp_type</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>samp_subtype</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>pressure</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>samp_tvdss</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>samp_md</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>oxy_stat_samp</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>samp_transport_cond</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>org_count_qpcr_info</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ph</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>alkalinity</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>alkalinity_method</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>sulfate</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>sulfide</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>tot_sulfur</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>nitrate</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>nitrite</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>ammonium</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>tot_nitro</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>diss_iron</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>sodium</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>chloride</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>potassium</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>magnesium</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>calcium</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>tot_iron</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>diss_org_carb</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>diss_inorg_carb</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>diss_inorg_phosp</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>tot_phosp</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>suspend_solids</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>density</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>diss_carb_dioxide</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>diss_oxygen_fluid</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>vfa</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>benzene</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>toluene</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>ethylbenzene</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>xylene</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>tan</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>viscosity</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>pour_point</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>saturates_pc</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>aromatics_pc</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>resins_pc</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>asphaltenes_pc</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>additional_info</t>
         </is>
@@ -1138,46 +1148,46 @@
     <dataValidation sqref="AI2:AI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT2:AT1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"flow cytometric cell sorting,lazer-tweezing,microfluidics,micromanipulation,optical manipulation,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AY2:AY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"mda based,pcr based"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="BB2:BB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BD2:BD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"chemical,combination,enzymatic,physical"</formula1>
     </dataValidation>
-    <dataValidation sqref="BL2:BL1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BN2:BN1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Coalbed,Gas Reservoir,Oil Reservoir,Oil Sand,Shale,Tight Gas Reservoir,Tight Oil Reservoir,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="BM2:BM1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BO2:BO1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bitumen,Coalbed Methane,Gas,Gas-Condensate,Oil,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="BW2:BW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BY2:BY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Basement,Chalk,Chert,Coal,Conglomerate,Diatomite,Dolomite,Limestone,Sandstone,Shale,Siltstone,Volcanic,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="BY2:BY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CA2:CA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Archean,Cambrian,Carboniferous,Cenozoic,Cretaceous,Devonian,Jurassic,Mesozoic,Neogene,Ordovician,Paleogene,Paleozoic,Permian,Precambrian,Proterozoic,Silurian,Triassic,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="CD2:CD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CF2:CF1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Type I,Type II,Type III,Type IV,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="CE2:CE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CG2:CG1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Biosilicieous,Carbonate,Clastic,Coal,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="CF2:CF1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CH2:CH1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fluvioldeltaic,Fluviomarine,Lacustine,Marine,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="CG2:CG1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CI2:CI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Archean,Cambrian,Carboniferous,Cenozoic,Cretaceous,Devonian,Jurassic,Mesozoic,Neogene,Ordovician,Paleogene,Paleozoic,Permian,Precambrian,Proterozoic,Silurian,Triassic,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="CK2:CK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CM2:CM1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"biofilm,not applicable,oil phase,other,water phase"</formula1>
     </dataValidation>
-    <dataValidation sqref="CO2:CO1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CQ2:CQ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"aerobic,anaerobic,other"</formula1>
     </dataValidation>
   </dataValidations>
